--- a/auditoria_brums_hiit/pipeline/exemplo_saidas/BRUMS_HIIT_resultados.xlsx
+++ b/auditoria_brums_hiit/pipeline/exemplo_saidas/BRUMS_HIIT_resultados.xlsx
@@ -59626,7 +59626,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>176.4</v>
+        <v>183.8</v>
       </c>
       <c r="C2" t="n">
         <v>6.6</v>
@@ -59642,7 +59642,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>175.2</v>
+        <v>183.3</v>
       </c>
       <c r="C3" t="n">
         <v>6.5</v>
@@ -59658,7 +59658,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>172.4</v>
+        <v>180.8</v>
       </c>
       <c r="C4" t="n">
         <v>7.1</v>
@@ -59674,7 +59674,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>175.2</v>
+        <v>183</v>
       </c>
       <c r="C5" t="n">
         <v>6.5</v>
